--- a/data/trans_orig/P6703-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6703-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene tiempo de llevar al día su trabajo en 2012</t>
+          <t>Población según si tiene tiempo de llevar al día su trabajo en 2012 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>25174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>28131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50145</t>
+          <t>51841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>28246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44155</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71718</t>
+          <t>71285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36814</t>
+          <t>36081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61228</t>
+          <t>61905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>20221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39576</t>
+          <t>40196</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62379</t>
+          <t>62724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93209</t>
+          <t>94191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76041</t>
+          <t>75464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103160</t>
+          <t>103232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61402</t>
+          <t>61605</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85491</t>
+          <t>85615</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144950</t>
+          <t>145642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179077</t>
+          <t>180896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,83%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23283</t>
+          <t>23178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20393</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43170</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>10344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>26902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51889</t>
+          <t>52814</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146929</t>
+          <t>144475</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>193364</t>
+          <t>195164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86480</t>
+          <t>86823</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>126892</t>
+          <t>125130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>242471</t>
+          <t>238771</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303159</t>
+          <t>302308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>245226</t>
+          <t>245231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>299739</t>
+          <t>298740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>158604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204047</t>
+          <t>204528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418282</t>
+          <t>416037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>488999</t>
+          <t>488959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>408243</t>
+          <t>409769</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>470010</t>
+          <t>473142</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229136</t>
+          <t>228959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>278178</t>
+          <t>279749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>653168</t>
+          <t>654023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734599</t>
+          <t>737269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20696</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,47 +2224,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7386</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3099</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>14240</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7386</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3135</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13998</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>47807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78610</t>
+          <t>77383</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65324</t>
+          <t>64056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92226</t>
+          <t>94158</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134070</t>
+          <t>133144</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89677</t>
+          <t>88116</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124581</t>
+          <t>122787</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54140</t>
+          <t>54772</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85541</t>
+          <t>88490</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>149838</t>
+          <t>151200</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>196752</t>
+          <t>197960</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113978</t>
+          <t>115158</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151322</t>
+          <t>151368</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90356</t>
+          <t>89574</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123153</t>
+          <t>121934</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>214142</t>
+          <t>213002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>264108</t>
+          <t>263342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>18727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40120</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43841</t>
+          <t>44004</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>44768</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74404</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24012</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48398</t>
+          <t>49415</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23816</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>45487</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52250</t>
+          <t>53021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85992</t>
+          <t>85719</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>237849</t>
+          <t>238967</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>297513</t>
+          <t>302800</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>150609</t>
+          <t>149536</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>196270</t>
+          <t>200152</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>406710</t>
+          <t>402604</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>479929</t>
+          <t>481214</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>390643</t>
+          <t>390276</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>462401</t>
+          <t>461812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>250091</t>
+          <t>249896</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>310977</t>
+          <t>309672</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>658821</t>
+          <t>658744</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>749104</t>
+          <t>753513</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>624539</t>
+          <t>623768</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>702862</t>
+          <t>700674</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>401050</t>
+          <t>398894</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>463053</t>
+          <t>463878</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1042615</t>
+          <t>1046472</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1142039</t>
+          <t>1150544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene tiempo de llevar al día su trabajo en 2016</t>
+          <t>Población según si tiene tiempo de llevar al día su trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15866</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>45341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21218</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60565</t>
+          <t>59548</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27011</t>
+          <t>27628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49061</t>
+          <t>49265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29629</t>
+          <t>30043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45464</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71987</t>
+          <t>72704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41533</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65483</t>
+          <t>66644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23333</t>
+          <t>23814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40372</t>
+          <t>39835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71538</t>
+          <t>70345</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101642</t>
+          <t>99047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39871</t>
+          <t>39615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37507</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41059</t>
+          <t>40105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69421</t>
+          <t>71091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55164</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28502</t>
+          <t>29142</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54187</t>
+          <t>55624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64566</t>
+          <t>65650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99447</t>
+          <t>99586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152030</t>
+          <t>154553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200389</t>
+          <t>200855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86692</t>
+          <t>87669</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124540</t>
+          <t>124966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252308</t>
+          <t>252078</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>311898</t>
+          <t>309988</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>279345</t>
+          <t>279334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>337778</t>
+          <t>339448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172804</t>
+          <t>174144</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216271</t>
+          <t>221743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>468716</t>
+          <t>469576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>543865</t>
+          <t>544378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342863</t>
+          <t>341748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>403389</t>
+          <t>406248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257466</t>
+          <t>259981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>309401</t>
+          <t>310451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>615102</t>
+          <t>616384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>697700</t>
+          <t>699304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15050</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26098</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31257</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24735</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26393</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50685</t>
+          <t>50936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46640</t>
+          <t>45787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75640</t>
+          <t>73725</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41436</t>
+          <t>41081</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68096</t>
+          <t>69672</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93256</t>
+          <t>92708</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>132344</t>
+          <t>133831</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>102450</t>
+          <t>101714</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>138596</t>
+          <t>139512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75527</t>
+          <t>75606</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108319</t>
+          <t>109018</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186550</t>
+          <t>186191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234648</t>
+          <t>236467</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123411</t>
+          <t>123875</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162025</t>
+          <t>162852</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>122478</t>
+          <t>120777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156548</t>
+          <t>158088</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259133</t>
+          <t>259007</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>309938</t>
+          <t>312058</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28882</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>57615</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26164</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49137</t>
+          <t>50179</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60883</t>
+          <t>61525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95411</t>
+          <t>95573</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58379</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92234</t>
+          <t>94450</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45757</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77249</t>
+          <t>77330</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>111649</t>
+          <t>110852</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>157091</t>
+          <t>158948</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>236570</t>
+          <t>238927</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>298042</t>
+          <t>299314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>148398</t>
+          <t>151058</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>199219</t>
+          <t>196473</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>404778</t>
+          <t>400197</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>479181</t>
+          <t>478508</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>427310</t>
+          <t>430840</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>500297</t>
+          <t>504929</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>279055</t>
+          <t>281854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>338384</t>
+          <t>339302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>734275</t>
+          <t>733129</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>829590</t>
+          <t>828000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>536723</t>
+          <t>533612</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>607499</t>
+          <t>609567</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>422912</t>
+          <t>422107</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>488043</t>
+          <t>484587</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>972058</t>
+          <t>972904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1068932</t>
+          <t>1078605</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene tiempo de llevar al día su trabajo en 2023</t>
+          <t>Población según si tiene tiempo de llevar al día su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,62 +6685,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5349</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5172</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>22121</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29032</t>
+          <t>29531</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,74%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31804</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47399</t>
+          <t>49178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50230</t>
+          <t>48789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102864</t>
+          <t>102497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29023</t>
+          <t>28256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47563</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36105</t>
+          <t>36061</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137649</t>
+          <t>138558</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23019</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149167</t>
+          <t>150102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50003</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74705</t>
+          <t>76342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>60201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212646</t>
+          <t>212860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211113</t>
+          <t>206010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>459644</t>
+          <t>466171</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100294</t>
+          <t>99585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127654</t>
+          <t>127000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329488</t>
+          <t>330130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>633334</t>
+          <t>620803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12202</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>30355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7251</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35455</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34151</t>
+          <t>33616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57929</t>
+          <t>55784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16010</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>18698</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>34336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39116</t>
+          <t>39658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64337</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43112</t>
+          <t>42408</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69323</t>
+          <t>67082</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38905</t>
+          <t>39499</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57392</t>
+          <t>57558</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87511</t>
+          <t>88470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119936</t>
+          <t>119650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>42936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56587</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51228</t>
+          <t>52312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>64455</t>
+          <t>63102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27211</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>134715</t>
+          <t>136054</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51313</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74273</t>
+          <t>74222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>69456</t>
+          <t>69638</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>197476</t>
+          <t>193465</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33395</t>
+          <t>42424</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>182266</t>
+          <t>184858</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78386</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107216</t>
+          <t>108230</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106653</t>
+          <t>91580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274500</t>
+          <t>271984</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>279195</t>
+          <t>277539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>583669</t>
+          <t>574769</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153154</t>
+          <t>153925</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187169</t>
+          <t>186984</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>452005</t>
+          <t>457168</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>803919</t>
+          <t>829076</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6703-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6703-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18792</t>
+          <t>19785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25174</t>
+          <t>25778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>28644</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51841</t>
+          <t>51662</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>10818</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>27470</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>44278</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71285</t>
+          <t>72791</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36081</t>
+          <t>36501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20221</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40196</t>
+          <t>39395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62724</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94191</t>
+          <t>94575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75464</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103232</t>
+          <t>103369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61605</t>
+          <t>59936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>84231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145642</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180896</t>
+          <t>180159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23178</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26993</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21295</t>
+          <t>21797</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44251</t>
+          <t>45129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>25975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52814</t>
+          <t>50752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144475</t>
+          <t>145404</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>195164</t>
+          <t>193711</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86823</t>
+          <t>86666</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>125130</t>
+          <t>127292</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>238771</t>
+          <t>243110</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>302308</t>
+          <t>307269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>245231</t>
+          <t>242000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298740</t>
+          <t>300223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158604</t>
+          <t>159463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204528</t>
+          <t>203337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416037</t>
+          <t>416553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>488959</t>
+          <t>488417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>409769</t>
+          <t>409866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>473142</t>
+          <t>474664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228959</t>
+          <t>227720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>279749</t>
+          <t>277499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>654023</t>
+          <t>651468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>737269</t>
+          <t>730595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27143</t>
+          <t>27474</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47807</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77383</t>
+          <t>78562</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37786</t>
+          <t>38082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64056</t>
+          <t>64515</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>94158</t>
+          <t>94159</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133144</t>
+          <t>133325</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88116</t>
+          <t>88661</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>122787</t>
+          <t>125114</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54772</t>
+          <t>55904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88490</t>
+          <t>85512</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>151200</t>
+          <t>152304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197960</t>
+          <t>197839</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115158</t>
+          <t>114393</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151368</t>
+          <t>153762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89574</t>
+          <t>88403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121934</t>
+          <t>121588</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>213002</t>
+          <t>213224</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>263342</t>
+          <t>260337</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41392</t>
+          <t>39432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44004</t>
+          <t>44972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44768</t>
+          <t>42920</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>75063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49415</t>
+          <t>47903</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45487</t>
+          <t>46630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53021</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85719</t>
+          <t>86475</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>238967</t>
+          <t>241109</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>302800</t>
+          <t>300757</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>149536</t>
+          <t>150639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>200152</t>
+          <t>200291</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>402604</t>
+          <t>405918</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>481214</t>
+          <t>483130</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>390276</t>
+          <t>387627</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>461812</t>
+          <t>462234</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>249896</t>
+          <t>250904</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>309672</t>
+          <t>310663</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>658744</t>
+          <t>659579</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>753513</t>
+          <t>754507</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>623768</t>
+          <t>621093</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>700674</t>
+          <t>698124</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>398894</t>
+          <t>401763</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>463878</t>
+          <t>466407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1046472</t>
+          <t>1045648</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1150544</t>
+          <t>1143697</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21218</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>25090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45341</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>34905</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59548</t>
+          <t>60291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49265</t>
+          <t>48813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>29659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46263</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72704</t>
+          <t>71946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>42698</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66644</t>
+          <t>66335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23814</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39835</t>
+          <t>39243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70345</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99047</t>
+          <t>100302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,61%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39615</t>
+          <t>40132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37958</t>
+          <t>39257</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40105</t>
+          <t>40600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71091</t>
+          <t>68923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>29927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54328</t>
+          <t>55833</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55624</t>
+          <t>55145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65650</t>
+          <t>65192</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99586</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>154553</t>
+          <t>154265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200855</t>
+          <t>201158</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>87669</t>
+          <t>86991</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124966</t>
+          <t>127632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>252078</t>
+          <t>252384</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>309988</t>
+          <t>314167</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>279334</t>
+          <t>280359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>339448</t>
+          <t>337188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174144</t>
+          <t>174431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>221743</t>
+          <t>221464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>469576</t>
+          <t>464121</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>544378</t>
+          <t>543439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341748</t>
+          <t>342933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>406248</t>
+          <t>403879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259981</t>
+          <t>256876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>310451</t>
+          <t>309087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>616384</t>
+          <t>620360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699304</t>
+          <t>699956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,36%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33835</t>
+          <t>31426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25410</t>
+          <t>24571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25537</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50936</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45787</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>74152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41081</t>
+          <t>41683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69672</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92708</t>
+          <t>94364</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133831</t>
+          <t>134326</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101714</t>
+          <t>99668</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>139512</t>
+          <t>137251</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75606</t>
+          <t>75007</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109018</t>
+          <t>109197</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>188256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>236467</t>
+          <t>236359</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123875</t>
+          <t>123184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162852</t>
+          <t>163384</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120777</t>
+          <t>122762</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158088</t>
+          <t>156481</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259007</t>
+          <t>257442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>312058</t>
+          <t>307717</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,69%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29156</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26011</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50179</t>
+          <t>50052</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61525</t>
+          <t>60726</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>97850</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>57896</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94450</t>
+          <t>93327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47398</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77330</t>
+          <t>76358</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>110852</t>
+          <t>113532</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>158948</t>
+          <t>159298</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>238927</t>
+          <t>239100</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>299314</t>
+          <t>299764</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>151058</t>
+          <t>148362</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>196473</t>
+          <t>197242</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>400197</t>
+          <t>404917</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>478508</t>
+          <t>486552</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>430840</t>
+          <t>430695</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>504929</t>
+          <t>502074</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>281854</t>
+          <t>281193</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>339302</t>
+          <t>340803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>733129</t>
+          <t>728545</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>828000</t>
+          <t>819318</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>533612</t>
+          <t>530682</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>609567</t>
+          <t>611754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>422107</t>
+          <t>422999</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>484587</t>
+          <t>488366</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>972904</t>
+          <t>970519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1078605</t>
+          <t>1067996</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,55%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>633</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -7097,32 +7097,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14589</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>29232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7132,32 +7132,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>9625</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>31416</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>22694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>40667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>9586</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18799</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>12864</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17573</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22111</t>
+          <t>22326</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49178</t>
+          <t>34043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,32 +7475,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7510,32 +7510,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>28934</t>
+          <t>30001</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48789</t>
+          <t>42664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>57644</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>43138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102497</t>
+          <t>74349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37606</t>
+          <t>40203</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47398</t>
+          <t>51310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87263</t>
+          <t>97847</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36061</t>
+          <t>81745</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>138558</t>
+          <t>119864</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73207</t>
+          <t>77573</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>61145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150102</t>
+          <t>94829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61901</t>
+          <t>70018</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50896</t>
+          <t>57692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76342</t>
+          <t>84860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>135108</t>
+          <t>147590</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>126956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212860</t>
+          <t>169601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>359856</t>
+          <t>130275</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>206010</t>
+          <t>112943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>466171</t>
+          <t>150383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>114172</t>
+          <t>125843</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99585</t>
+          <t>108990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127000</t>
+          <t>138795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>474028</t>
+          <t>256117</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330130</t>
+          <t>233865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>620803</t>
+          <t>284130</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>511804</t>
+          <t>297403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>231102</t>
+          <t>256603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>742906</t>
+          <t>554006</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>10473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30355</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,22 +8157,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22708</t>
+          <t>23821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>26697</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>43715</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33616</t>
+          <t>37211</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55784</t>
+          <t>61175</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24867</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>27020</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18698</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34336</t>
+          <t>35842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>50747</t>
+          <t>56120</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39658</t>
+          <t>43608</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65588</t>
+          <t>70976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>54885</t>
+          <t>60809</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>47214</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67082</t>
+          <t>76003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>48489</t>
+          <t>52318</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39499</t>
+          <t>42403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>61835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>103373</t>
+          <t>113127</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88470</t>
+          <t>95483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119650</t>
+          <t>129079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105701</t>
+          <t>115206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230916</t>
+          <t>255147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42936</t>
+          <t>44192</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>47199</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56767</t>
+          <t>66146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52312</t>
+          <t>42102</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63102</t>
+          <t>59905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>80207</t>
+          <t>90561</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>73277</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136054</t>
+          <t>110296</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61821</t>
+          <t>69983</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>142029</t>
+          <t>160544</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>69638</t>
+          <t>138873</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>193465</t>
+          <t>184675</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>109047</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>95798</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>184858</t>
+          <t>138153</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>91815</t>
+          <t>102347</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>108230</t>
+          <t>119784</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>200863</t>
+          <t>220185</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91580</t>
+          <t>192782</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271984</t>
+          <t>246890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>429329</t>
+          <t>212876</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277539</t>
+          <t>188758</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>574769</t>
+          <t>238508</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>170385</t>
+          <t>187785</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153925</t>
+          <t>170313</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>186984</t>
+          <t>206127</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>599714</t>
+          <t>400661</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>457168</t>
+          <t>368680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>829076</t>
+          <t>430473</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>669961</t>
+          <t>478773</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1024967</t>
+          <t>874201</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
